--- a/EKG_Kalite_Yönetim_Sistemi/06_Garanti Sorunları Yönetimi/01_WIM1 - Koordinatör, Portal ve İade Parça/EKG-KLT-LST-06_garanti_iade_parca_takip_ve_uzman_listesi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/06_Garanti Sorunları Yönetimi/01_WIM1 - Koordinatör, Portal ve İade Parça/EKG-KLT-LST-06_garanti_iade_parca_takip_ve_uzman_listesi.xlsx
@@ -895,7 +895,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-LST-06&amp;C&amp;"Arial,Regular"&amp;11Garanti İade Parça Takip ve Uzman Listesi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 21.09.2026
+Revizyon nedeni: Garanti numunesinin teslim zinciri ve rapor/karar izi eklendi; uzman kapsamı ve yetkinlik kaydına bağlandı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1025,7 +1026,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-LST-06&amp;C&amp;"Arial,Regular"&amp;11Garanti İade Parça Takip ve Uzman Listesi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 21.09.2026
+Revizyon nedeni: Garanti numunesinin teslim zinciri ve rapor/karar izi eklendi; uzman kapsamı ve yetkinlik kaydına bağlandı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>